--- a/Simulador_CashBack_Barter_2026.xlsx
+++ b/Simulador_CashBack_Barter_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://syngenta-my.sharepoint.com/personal/leonardo_vale_syngenta_com/Documents/Desktop/Lotes Barter/Safra_2026_27/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0e760a1110f3163/Projetos/Barter Simulator/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{4471872B-2932-4B94-9F5A-F15A4FAF387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFECC2ED-E5F5-42E4-8D98-4CFF7DB18D9C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4035" windowWidth="29040" windowHeight="15720" xr2:uid="{507E8C52-4AC5-4303-BA21-5B7B491348B3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{507E8C52-4AC5-4303-BA21-5B7B491348B3}"/>
   </bookViews>
   <sheets>
     <sheet name="R.T._usd" sheetId="1" r:id="rId1"/>
@@ -42,9 +42,9 @@
   <commentList>
     <comment ref="A9" authorId="0" shapeId="0" xr:uid="{ECE83973-34DB-4453-AA3D-71BBBD31F878}">
       <text>
-        <t xml:space="preserve">[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     SIM - Faturamento PF
 NÃO - Faturamento PJ
 Clientes que faturam algodão via cooperativa o pagamento sendo integral. </t>
@@ -52,9 +52,9 @@
     </comment>
     <comment ref="A13" authorId="1" shapeId="0" xr:uid="{D34899CD-80EE-484B-B161-619D1F68A27E}">
       <text>
-        <t xml:space="preserve">[Comentário encadeado]
-Sua versão do Excel permite que você leia este comentário encadeado, no entanto, as edições serão removidas se o arquivo for aberto em uma versão mais recente do Excel. Saiba mais: https://go.microsoft.com/fwlink/?linkid=870924
-Comentário:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Para entendermos o volume de kg no algodão, deve-se multiplicar por 15 a quantidade de @. </t>
       </text>
     </comment>
@@ -674,35 +674,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentagem" xfId="2" builtinId="5"/>
-    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -813,7 +813,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -1123,49 +1123,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54717C0C-3EA0-4673-B5FB-11A75A00A79B}">
   <dimension ref="A1:P33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" style="42" customWidth="1"/>
-    <col min="4" max="4" width="41.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.88671875" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" customWidth="1"/>
-    <col min="7" max="7" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.33203125" customWidth="1"/>
-    <col min="10" max="10" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.36328125" customWidth="1"/>
+    <col min="2" max="2" width="21.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" style="42" customWidth="1"/>
+    <col min="4" max="4" width="41.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.90625" customWidth="1"/>
+    <col min="6" max="6" width="9.6328125" customWidth="1"/>
+    <col min="7" max="7" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.36328125" customWidth="1"/>
+    <col min="10" max="10" width="29.08984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.36328125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="10" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.33203125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.36328125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
+      <c r="B1" s="58"/>
       <c r="C1" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="60"/>
+      <c r="E1" s="58"/>
       <c r="F1" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="60"/>
+      <c r="H1" s="58"/>
       <c r="I1" s="24"/>
-      <c r="J1" s="55" t="s">
+      <c r="J1" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="56"/>
+      <c r="K1" s="54"/>
       <c r="M1" t="s">
         <v>4</v>
       </c>
@@ -1181,7 +1181,7 @@
         <v>9.9600000000000008E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -1202,8 +1202,8 @@
       <c r="H2" s="34">
         <v>45931</v>
       </c>
-      <c r="J2" s="57"/>
-      <c r="K2" s="58"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="56"/>
       <c r="M2" t="s">
         <v>3</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>7.5200000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>47</v>
       </c>
@@ -1239,12 +1239,12 @@
       <c r="H3" s="35">
         <v>46147</v>
       </c>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="56"/>
       <c r="N3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>46</v>
       </c>
@@ -1266,8 +1266,8 @@
         <f>H3-H2</f>
         <v>216</v>
       </c>
-      <c r="J4" s="57"/>
-      <c r="K4" s="58"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="56"/>
       <c r="M4" t="s">
         <v>2</v>
       </c>
@@ -1283,7 +1283,7 @@
         <v>8.6400000000000005E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
@@ -1317,7 +1317,7 @@
       <c r="N5" s="1"/>
       <c r="P5" s="1"/>
     </row>
-    <row r="6" spans="1:16" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
@@ -1345,7 +1345,7 @@
       <c r="N6" s="1"/>
       <c r="P6" s="1"/>
     </row>
-    <row r="7" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="5"/>
       <c r="D7" s="2"/>
@@ -1362,7 +1362,7 @@
       <c r="N7" s="1"/>
       <c r="P7" s="1"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -1385,7 +1385,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -1404,7 +1404,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="31"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="K10" s="31"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>15</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>44</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="5"/>
       <c r="C14" s="44"/>
@@ -1521,20 +1521,20 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="53" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="54"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="44"/>
-      <c r="D15" s="53" t="s">
+      <c r="D15" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="54"/>
-      <c r="G15" s="53" t="s">
+      <c r="E15" s="60"/>
+      <c r="G15" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="H15" s="54"/>
+      <c r="H15" s="60"/>
       <c r="J15" s="2" t="s">
         <v>33</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>42</v>
       </c>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="K16" s="28"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="28"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>21</v>
       </c>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="K18" s="31"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="K19" s="28"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="18"/>
       <c r="D20" s="2"/>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="K20" s="28"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="K21" s="28"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K22" s="28"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="21"/>
       <c r="D23" s="2"/>
@@ -1739,21 +1739,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" s="53" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="D24" s="53" t="s">
+      <c r="B24" s="60"/>
+      <c r="D24" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="54"/>
+      <c r="E24" s="60"/>
       <c r="G24" s="2"/>
       <c r="H24" s="9"/>
       <c r="J24" s="2"/>
       <c r="K24" s="28"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
@@ -1773,7 +1773,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="28"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -1788,10 +1788,10 @@
         <f>E2*E25</f>
         <v>33136.966126656851</v>
       </c>
-      <c r="G26" s="53" t="s">
+      <c r="G26" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="54"/>
+      <c r="H26" s="60"/>
       <c r="J26" s="4" t="s">
         <v>37</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>22</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="9"/>
       <c r="D29" s="2"/>
@@ -1870,7 +1870,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="27"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
@@ -1890,7 +1890,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="27"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>22</v>
       </c>
@@ -1922,7 +1922,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="27"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>29</v>
       </c>
@@ -1955,7 +1955,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="27"/>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="11" t="s">
         <v>30</v>
       </c>
@@ -1985,16 +1985,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="J1:K4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="C13">
